--- a/data/processed/harmonization/Acidity__Soil_pH/10.15485_1647038/10.15485_1647038_soil_Acidity__Soil_pH.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/10.15485_1647038/10.15485_1647038_soil_Acidity__Soil_pH.xlsx
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HZ1:1</t>
+          <t>HZ1:2017-05-20:1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>XC1_Hn:4</t>
+          <t>XC1_Hn:2017-07-05:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>XC1_H1:6</t>
+          <t>XC1_H1:2017-07-06:6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>XC1_H2:7</t>
+          <t>XC1_H2:2017-07-06:7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>XC1_H2:8</t>
+          <t>XC1_H2:2017-07-06:8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>XC1_H3:9</t>
+          <t>XC1_H3:2017-07-06:9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:10</t>
+          <t>XC1_H4:2017-07-06:10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:11</t>
+          <t>XC1_H4:2017-07-06:11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:12</t>
+          <t>XC1_H4:2017-07-06:12</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:13</t>
+          <t>XC1_H4:2017-07-06:13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:14</t>
+          <t>XC1_H5:2017-07-10:14</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:15</t>
+          <t>XC1_H5:2017-07-10:15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:16</t>
+          <t>XC1_H5:2017-07-10:16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>XC1_H6:17</t>
+          <t>XC1_H6:2017-07-12:17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>XC1_H0:18</t>
+          <t>XC1_H0:2017-07-12:18</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>XC1_H0:19</t>
+          <t>XC1_H0:2017-07-14:19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>XC1_H0:20</t>
+          <t>XC1_H0:2017-07-14:20</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>XC1_H1:22</t>
+          <t>XC1_H1:2017-07-15:22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>XC1_H2:23</t>
+          <t>XC1_H2:2017-07-15:23</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>XC1_H2:24</t>
+          <t>XC1_H2:2017-07-15:24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:26</t>
+          <t>XC1_H4:2017-07-15:26</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:27</t>
+          <t>XC1_H4:2017-07-15:27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:28</t>
+          <t>XC1_H4:2017-07-15:28</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>XC1_H4:29</t>
+          <t>XC1_H4:2017-07-15:29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:32</t>
+          <t>XC1_H5:2017-07-16:32</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:33</t>
+          <t>XC1_H5:2017-07-16:33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>XC1_H5:34</t>
+          <t>XC1_H5:2017-07-16:34</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>XC1_H6:35</t>
+          <t>XC1_H6:2017-07-16:35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>XC1_H0:36</t>
+          <t>XC1_H0:2017-07-16:36</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>XC1_H0:37</t>
+          <t>XC1_H0:2017-07-16:37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>XC1_Hn:38</t>
+          <t>XC1_Hn:2017-07-16:38</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>HZ1:39</t>
+          <t>HZ1:2017-08-27:39</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>HZ1:40</t>
+          <t>HZ1:2017-08-27:40</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>HZ2:41</t>
+          <t>HZ2:2017-08-28:41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>HZ2:42</t>
+          <t>HZ2:2017-08-28:42</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>HZ2:43</t>
+          <t>HZ2:2017-08-28:43</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sample:id</t>
+          <t>Sample:date:id</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
